--- a/sheets/조재수대금교본/검수/남본청.xlsx
+++ b/sheets/조재수대금교본/검수/남본청.xlsx
@@ -2608,57 +2608,36 @@
     </row>
     <row r="5" ht="100.96" customHeight="true">
       <c r="A5" s="0"/>
-      <c r="B5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B5" s="21"/>
       <c r="C5" s="24"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D5" s="21"/>
       <c r="E5" s="24"/>
-      <c r="F5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F5" s="21"/>
       <c r="G5" s="24"/>
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-ﾉ
 潢</t>
         </is>
       </c>
       <c r="I5" s="24"/>
-      <c r="J5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J5" s="21"/>
       <c r="K5" s="24"/>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L5" s="21"/>
       <c r="M5" s="24"/>
     </row>
     <row r="6" ht="100.96" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼
+          <t xml:space="preserve">潢∼
 –南</t>
         </is>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -2676,13 +2655,13 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -2721,42 +2700,21 @@
     </row>
     <row r="8" ht="100.96" customHeight="true">
       <c r="A8" s="0"/>
-      <c r="B8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B8" s="21"/>
       <c r="C8" s="24"/>
-      <c r="D8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D8" s="21"/>
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="G8" s="24"/>
-      <c r="H8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H8" s="21"/>
       <c r="I8" s="24"/>
-      <c r="J8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J8" s="21"/>
       <c r="K8" s="24"/>
-      <c r="L8" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
     <row r="9" ht="100.96" customHeight="true">
@@ -2790,7 +2748,6 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
-ﾉ
 姑∼</t>
         </is>
       </c>
@@ -2805,11 +2762,7 @@
     </row>
     <row r="10" ht="100.96" customHeight="true">
       <c r="A10" s="0"/>
-      <c r="B10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="B10" s="21"/>
       <c r="C10" s="23"/>
       <c r="D10" s="21"/>
       <c r="E10" s="23"/>
@@ -2826,42 +2779,23 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="C11" s="24"/>
-      <c r="D11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ﾉ
-‹</t>
-        </is>
-      </c>
+      <c r="D11" s="21"/>
       <c r="E11" s="24"/>
-      <c r="F11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F11" s="21"/>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢⊏∼
-‹</t>
+          <t xml:space="preserve">潢∼</t>
         </is>
       </c>
       <c r="I11" s="24"/>
-      <c r="J11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J11" s="21"/>
       <c r="K11" s="24"/>
-      <c r="L11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L11" s="21"/>
       <c r="M11" s="24"/>
     </row>
     <row r="12" ht="100.96" customHeight="true">
@@ -2892,14 +2826,14 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c南南c
+          <t xml:space="preserve">南南
 姑</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">c南南c
+          <t xml:space="preserve">南南
 姑</t>
         </is>
       </c>
@@ -2937,35 +2871,15 @@
         </is>
       </c>
       <c r="C14" s="24"/>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D14" s="21"/>
       <c r="E14" s="24"/>
-      <c r="F14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F14" s="21"/>
       <c r="G14" s="24"/>
-      <c r="H14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H14" s="21"/>
       <c r="I14" s="24"/>
-      <c r="J14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J14" s="21"/>
       <c r="K14" s="24"/>
-      <c r="L14" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L14" s="21"/>
       <c r="M14" s="24"/>
     </row>
   </sheetData>

--- a/sheets/조재수대금교본/검수/남본청.xlsx
+++ b/sheets/조재수대금교본/검수/남본청.xlsx
@@ -2617,6 +2617,7 @@
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
+ﾉ
 潢</t>
         </is>
       </c>
@@ -2630,14 +2631,14 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼
+          <t xml:space="preserve">潢⊏∼
 –南</t>
         </is>
       </c>
       <c r="C6" s="22"/>
       <c r="D6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="E6" s="22"/>
@@ -2655,13 +2656,13 @@
       <c r="I6" s="22"/>
       <c r="J6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢⊏∼</t>
         </is>
       </c>
       <c r="K6" s="22"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢⊏∼</t>
         </is>
       </c>
       <c r="M6" s="22"/>
@@ -2706,7 +2707,7 @@
       <c r="E8" s="24"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢⊏∼</t>
         </is>
       </c>
       <c r="G8" s="24"/>
@@ -2748,6 +2749,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
+ﾉ
 姑∼</t>
         </is>
       </c>
@@ -2779,17 +2781,21 @@
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢⊏∼</t>
         </is>
       </c>
       <c r="C11" s="24"/>
-      <c r="D11" s="21"/>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ﾉ</t>
+        </is>
+      </c>
       <c r="E11" s="24"/>
       <c r="F11" s="21"/>
       <c r="G11" s="24"/>
       <c r="H11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢∼</t>
+          <t xml:space="preserve">潢⊏∼</t>
         </is>
       </c>
       <c r="I11" s="24"/>
@@ -2826,14 +2832,14 @@
       <c r="I12" s="22"/>
       <c r="J12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南
+          <t xml:space="preserve">c南南c
 姑</t>
         </is>
       </c>
       <c r="K12" s="22"/>
       <c r="L12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">南南
+          <t xml:space="preserve">c南南c
 姑</t>
         </is>
       </c>

--- a/sheets/조재수대금교본/검수/남본청.xlsx
+++ b/sheets/조재수대금교본/검수/남본청.xlsx
@@ -2512,24 +2512,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="16.2" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="16.2" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="16.2" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="16.2" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="16.2" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="16.2" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="67.8" customHeight="true">
+    <row r="2" ht="63.49" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="100.96" customHeight="true">
+    <row r="3" ht="94.52" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2591,7 +2591,7 @@
       </c>
       <c r="M3" s="22"/>
     </row>
-    <row r="4" ht="100.96" customHeight="true">
+    <row r="4" ht="94.52" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="23"/>
@@ -2606,7 +2606,7 @@
       <c r="L4" s="21"/>
       <c r="M4" s="23"/>
     </row>
-    <row r="5" ht="100.96" customHeight="true">
+    <row r="5" ht="94.52" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="24"/>
@@ -2627,7 +2627,7 @@
       <c r="L5" s="21"/>
       <c r="M5" s="24"/>
     </row>
-    <row r="6" ht="100.96" customHeight="true">
+    <row r="6" ht="94.52" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="M6" s="22"/>
     </row>
-    <row r="7" ht="100.96" customHeight="true">
+    <row r="7" ht="94.52" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
       </c>
       <c r="M7" s="23"/>
     </row>
-    <row r="8" ht="100.96" customHeight="true">
+    <row r="8" ht="94.52" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="24"/>
@@ -2718,7 +2718,7 @@
       <c r="L8" s="21"/>
       <c r="M8" s="24"/>
     </row>
-    <row r="9" ht="100.96" customHeight="true">
+    <row r="9" ht="94.52" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="M9" s="22"/>
     </row>
-    <row r="10" ht="100.96" customHeight="true">
+    <row r="10" ht="94.52" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="23"/>
@@ -2777,7 +2777,7 @@
       <c r="L10" s="21"/>
       <c r="M10" s="23"/>
     </row>
-    <row r="11" ht="100.96" customHeight="true">
+    <row r="11" ht="94.52" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2804,7 +2804,7 @@
       <c r="L11" s="21"/>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="100.96" customHeight="true">
+    <row r="12" ht="94.52" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="M12" s="22"/>
     </row>
-    <row r="13" ht="100.96" customHeight="true">
+    <row r="13" ht="94.52" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="23"/>
@@ -2868,7 +2868,7 @@
       </c>
       <c r="M13" s="23"/>
     </row>
-    <row r="14" ht="100.96" customHeight="true">
+    <row r="14" ht="94.52" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2894,6 +2894,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="59"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="63"/>
 </worksheet>
 </file>